--- a/大會師總戰報_20260610/🎨_全策略大會師總表_20260610.xlsx
+++ b/大會師總戰報_20260610/🎨_全策略大會師總表_20260610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,217 +478,1054 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3710.TWO</t>
+          <t>6186.TWO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>連展投控</t>
+          <t>新潤</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>老余裸K</t>
+          <t>四均線起漲精選 | 回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.99</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="F2" t="n">
-        <v>603</v>
+        <v>3530</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4123.TWO</t>
+          <t>2348.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>海悅</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>老余裸K</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>37.95</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>13.9</v>
       </c>
       <c r="F3" t="n">
-        <v>2155</v>
+        <v>5906</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4714.TWO</t>
+          <t>6180.TWO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>永捷</t>
+          <t>橘子</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>老余裸K</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.5</v>
+        <v>47.05</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="F4" t="n">
-        <v>1840</v>
+        <v>2508</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4745.TWO</t>
+          <t>2913.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>合富-KY</t>
+          <t>農林</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>老余裸K</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.5</v>
+        <v>11.45</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="F5" t="n">
-        <v>1248</v>
+        <v>12425</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6186.TWO</t>
+          <t>2537.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新潤</t>
+          <t>聯上發</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>四均線起漲精選</t>
+          <t>四均線起漲精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="F6" t="n">
-        <v>3530</v>
+        <v>9519</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7717.TWO</t>
+          <t>5508.TWO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>永信建</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>老余裸K</t>
+          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>57.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="n">
-        <v>677</v>
+        <v>2928</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8034.TWO</t>
+          <t>1736.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>老余裸K</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23.4</v>
+        <v>112</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>518</v>
+        <v>1182</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1225.TW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>福懋油</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>527</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2243.TW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>宏旭-KY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2126</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2208.TW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>台船</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2631</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2530.TW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>華建</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2287</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2540.TW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>愛山林</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4214</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2548.TW</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>華固</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8421</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3576.TW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>聯合再生</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>57171</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3710.TWO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>連展投控</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>603</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2413.TW</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>環科</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>21255</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2528.TW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>皇普</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1795.TW</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>美時</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>202</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2502</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4560.TW</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>強信-KY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>544</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4123.TWO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>晟德</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2155</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4119.TW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>旭富</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>719</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4564.TW</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>元翎</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>919</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4934.TW</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>太極</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1904</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5213.TWO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>亞昕</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1321</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4745.TWO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>合富-KY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4714.TWO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>永捷</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1840</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5521.TW</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>工信</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10151</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5258.TW</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>虹堡</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>610</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5534.TW</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>長虹</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>四均線起漲精選</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7386</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7717.TWO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>萊德光電-KY</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>654</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>677</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7788.TW</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>松川精密</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3256</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8034.TWO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>榮群</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>518</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8476.TW</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>台境*</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2794</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9940.TW</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>信義</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>四均線起漲精選</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2251</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
         <v>1</v>
       </c>
     </row>

--- a/大會師總戰報_20260610/🎨_全策略大會師總表_20260610.xlsx
+++ b/大會師總戰報_20260610/🎨_全策略大會師總表_20260610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6186.TWO</t>
+          <t>2913.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>新潤</t>
+          <t>農林</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>四均線起漲精選 | 回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
+          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>11.45</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="F2" t="n">
-        <v>3530</v>
+        <v>12425</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -540,12 +540,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6180.TWO</t>
+          <t>6186.TWO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>橘子</t>
+          <t>新潤</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47.05</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2508</v>
+        <v>3530</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -571,12 +571,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2913.TW</t>
+          <t>6180.TWO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>農林</t>
+          <t>橘子</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.45</v>
+        <v>47.05</v>
       </c>
       <c r="E5" t="n">
-        <v>8.4</v>
+        <v>2.7</v>
       </c>
       <c r="F5" t="n">
-        <v>12425</v>
+        <v>2508</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -602,27 +602,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2537.TW</t>
+          <t>5508.TWO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯上發</t>
+          <t>永信建</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>四均線起漲精選 | 回後買上漲基礎版</t>
+          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>57.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="n">
-        <v>9519</v>
+        <v>2928</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -633,58 +633,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5508.TWO</t>
+          <t>1736.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>永信建</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>57.5</v>
+        <v>112</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>2928</v>
+        <v>1182</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1736.TW</t>
+          <t>2472.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>喬山</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>112</v>
+        <v>372.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1182</v>
+        <v>2386</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -726,27 +726,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2243.TW</t>
+          <t>2208.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>宏旭-KY</t>
+          <t>台船</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30.8</v>
+        <v>17.85</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2126</v>
+        <v>2631</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -757,12 +757,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2208.TW</t>
+          <t>1795.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台船</t>
+          <t>美時</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.85</v>
+        <v>202</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>2631</v>
+        <v>2502</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -788,27 +788,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2530.TW</t>
+          <t>2497.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華建</t>
+          <t>怡利電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20.25</v>
+        <v>65.8</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="F12" t="n">
-        <v>2287</v>
+        <v>2159</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -819,12 +819,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2540.TW</t>
+          <t>2528.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>愛山林</t>
+          <t>皇普</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55.3</v>
+        <v>22.35</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>4214</v>
+        <v>1430</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -850,27 +850,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2548.TW</t>
+          <t>2537.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>華固</t>
+          <t>聯上發</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>105.5</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="F14" t="n">
-        <v>8421</v>
+        <v>9519</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -881,27 +881,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3576.TW</t>
+          <t>2530.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>聯合再生</t>
+          <t>華建</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.25</v>
+        <v>20.25</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="F15" t="n">
-        <v>57171</v>
+        <v>2287</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -912,27 +912,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3710.TWO</t>
+          <t>2540.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>連展投控</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.99</v>
+        <v>55.3</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>603</v>
+        <v>4214</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -943,27 +943,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2413.TW</t>
+          <t>2476.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>環科</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59.6</v>
+        <v>125.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="n">
-        <v>21255</v>
+        <v>6428</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -974,27 +974,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2528.TW</t>
+          <t>2484.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>皇普</t>
+          <t>希華</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22.35</v>
+        <v>60.8</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="F18" t="n">
-        <v>1430</v>
+        <v>60687</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1005,27 +1005,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1795.TW</t>
+          <t>2413.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>美時</t>
+          <t>環科</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>202</v>
+        <v>59.6</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="F19" t="n">
-        <v>2502</v>
+        <v>21255</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1036,27 +1036,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4560.TW</t>
+          <t>2891.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>強信-KY</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>32.45</v>
+        <v>69.2</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F20" t="n">
-        <v>544</v>
+        <v>53423</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1067,27 +1067,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4123.TWO</t>
+          <t>2836.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>高雄銀</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>四均線起漲精選</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37.95</v>
+        <v>12.35</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="F21" t="n">
-        <v>2155</v>
+        <v>10611</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4119.TW</t>
+          <t>2548.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>旭富</t>
+          <t>華固</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.95</v>
+        <v>105.5</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>719</v>
+        <v>8421</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -1129,27 +1129,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4564.TW</t>
+          <t>3003.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>元翎</t>
+          <t>健和興</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.15</v>
+        <v>64.2</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F23" t="n">
-        <v>919</v>
+        <v>1808</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1160,27 +1160,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4934.TW</t>
+          <t>3479.TWO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>安勤</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.25</v>
+        <v>125.5</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="F24" t="n">
-        <v>1904</v>
+        <v>1260</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1191,27 +1191,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5213.TWO</t>
+          <t>3044.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>亞昕</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>23.7</v>
+        <v>500</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1321</v>
+        <v>4547</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1222,27 +1222,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4745.TWO</t>
+          <t>3162.TWO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>合富-KY</t>
+          <t>精確</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.5</v>
+        <v>87</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="F26" t="n">
-        <v>1248</v>
+        <v>5440</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1253,27 +1253,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4714.TWO</t>
+          <t>3221.TWO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>永捷</t>
+          <t>台嘉碩</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.5</v>
+        <v>63.9</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>1840</v>
+        <v>28407</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1284,27 +1284,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5521.TW</t>
+          <t>4123.TWO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>工信</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.25</v>
+        <v>37.95</v>
       </c>
       <c r="E28" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>10151</v>
+        <v>2155</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1315,12 +1315,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5258.TW</t>
+          <t>4560.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>強信-KY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>48.85</v>
+        <v>32.45</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>610</v>
+        <v>544</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1346,27 +1346,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5534.TW</t>
+          <t>4564.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>長虹</t>
+          <t>元翎</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>四均線起漲精選</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>83.5</v>
+        <v>15.15</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>7386</v>
+        <v>919</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1377,12 +1377,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7717.TWO</t>
+          <t>4714.TWO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>永捷</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1391,13 +1391,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>654</v>
+        <v>13.5</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>677</v>
+        <v>1840</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1408,27 +1408,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7788.TW</t>
+          <t>4721.TWO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>美琪瑪</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>258.5</v>
+        <v>94.5</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="F32" t="n">
-        <v>3256</v>
+        <v>2999</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -1439,12 +1439,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8034.TWO</t>
+          <t>3710.TWO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>連展投控</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>23.4</v>
+        <v>5.99</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>518</v>
+        <v>603</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -1470,27 +1470,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8476.TW</t>
+          <t>3715.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19.05</v>
+        <v>174.5</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>2794</v>
+        <v>15834</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1501,31 +1501,527 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9940.TW</t>
+          <t>4119.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>信義</t>
+          <t>旭富</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>四均線起漲精選</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>19.55</v>
+        <v>42.95</v>
       </c>
       <c r="E35" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>2251</v>
+        <v>719</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5213.TWO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>亞昕</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1321</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4934.TW</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>太極</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1904</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4745.TWO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>合富-KY</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5258.TW</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>虹堡</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>610</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>6156.TWO</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>松上</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>538</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>5386.TWO</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>548</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1841</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6166.TW</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>凌華</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2916</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6274.TWO</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1615</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8707</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6279.TWO</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>胡連</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1391</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6414.TW</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>樺漢</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>401</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3363</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6831.TW</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>邁科</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>776</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1772</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>7777.TWO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>能率亞洲</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3162</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>7788.TW</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>松川精密</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3256</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8050.TWO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>廣積</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1641</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>8110.TW</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>華東</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10206</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>8476.TW</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>台境*</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2794</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
         <v>1</v>
       </c>
     </row>
